--- a/artfynd/A 56047-2025 artfynd.xlsx
+++ b/artfynd/A 56047-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1011,15 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113768313</v>
+        <v>129985216</v>
       </c>
       <c r="B5" t="n">
-        <v>57412</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,7 +1041,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -1055,17 +1050,17 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Slättåkra (Slättåkra), Sk</t>
+          <t>Ljungby, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>388253</v>
+        <v>388160</v>
       </c>
       <c r="R5" t="n">
-        <v>6213724</v>
+        <v>6213675</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1089,12 +1084,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-12-27</t>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-12-27</t>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,44 +1114,39 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Bengt  Bengtsson</t>
+          <t>Per Muhr</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Bengt  Bengtsson</t>
+          <t>Per Muhr, Inger Persson, Petra Borgcrantz, Thomas Arnström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113768343</v>
+        <v>129997570</v>
       </c>
       <c r="B6" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57893</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103020</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1156,26 +1156,30 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Slättåkra (Slättåkra), Sk</t>
+          <t>Slättåkra alsumpskog A56047-2025, Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>388189</v>
+        <v>388121</v>
       </c>
       <c r="R6" t="n">
-        <v>6213746</v>
+        <v>6213608</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1199,12 +1203,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-12-27</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-12-27</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1219,15 +1223,585 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129985213</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57750</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ljungby, Sk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>388160</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6213675</v>
+      </c>
+      <c r="S7" t="n">
+        <v>78</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Riseberga</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Högstubbar med bohål</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Per Muhr, Inger Persson, Petra Borgcrantz, Thomas Arnström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129985211</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57674</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100082</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Röd glada</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Milvus milvus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ljungby, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>388160</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6213675</v>
+      </c>
+      <c r="S8" t="n">
+        <v>78</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Riseberga</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Per Muhr, Inger Persson, Petra Borgcrantz, Thomas Arnström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129985220</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58416</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ljungby, Sk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>388160</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6213675</v>
+      </c>
+      <c r="S9" t="n">
+        <v>78</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Riseberga</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-12-05</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Per Muhr</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Per Muhr, Inger Persson, Petra Borgcrantz, Thomas Arnström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>113768313</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57412</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Slättåkra (Slättåkra), Sk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>388253</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6213724</v>
+      </c>
+      <c r="S10" t="n">
+        <v>50</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Riseberga</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-12-27</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-12-27</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Bengt  Bengtsson</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Bengt  Bengtsson</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>113768343</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57624</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Slättåkra (Slättåkra), Sk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>388189</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6213746</v>
+      </c>
+      <c r="S11" t="n">
+        <v>50</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Riseberga</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-12-27</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-12-27</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Bengt  Bengtsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Bengt  Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56047-2025 artfynd.xlsx
+++ b/artfynd/A 56047-2025 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>129985216</v>
       </c>
       <c r="B5" t="n">
-        <v>57893</v>
+        <v>57896</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Per Muhr, Inger Persson, Petra Borgcrantz, Thomas Arnström</t>
+          <t>Thomas Arnström, Petra Borgcrantz, Inger Persson, Per Muhr</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1129,7 +1129,7 @@
         <v>129997570</v>
       </c>
       <c r="B6" t="n">
-        <v>57893</v>
+        <v>57896</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>129985213</v>
       </c>
       <c r="B7" t="n">
-        <v>57750</v>
+        <v>57753</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Per Muhr, Inger Persson, Petra Borgcrantz, Thomas Arnström</t>
+          <t>Thomas Arnström, Petra Borgcrantz, Inger Persson, Per Muhr</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1358,7 +1358,7 @@
         <v>129985211</v>
       </c>
       <c r="B8" t="n">
-        <v>57674</v>
+        <v>57677</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Per Muhr, Inger Persson, Petra Borgcrantz, Thomas Arnström</t>
+          <t>Thomas Arnström, Petra Borgcrantz, Inger Persson, Per Muhr</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
         <v>129985220</v>
       </c>
       <c r="B9" t="n">
-        <v>58416</v>
+        <v>58419</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Per Muhr, Inger Persson, Petra Borgcrantz, Thomas Arnström</t>
+          <t>Thomas Arnström, Petra Borgcrantz, Inger Persson, Per Muhr</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 56047-2025 artfynd.xlsx
+++ b/artfynd/A 56047-2025 artfynd.xlsx
@@ -1119,7 +1119,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Thomas Arnström, Petra Borgcrantz, Inger Persson, Per Muhr</t>
+          <t>Per Muhr, Inger Persson, Petra Borgcrantz, Thomas Arnström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Thomas Arnström, Petra Borgcrantz, Inger Persson, Per Muhr</t>
+          <t>Per Muhr, Inger Persson, Petra Borgcrantz, Thomas Arnström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Thomas Arnström, Petra Borgcrantz, Inger Persson, Per Muhr</t>
+          <t>Per Muhr, Inger Persson, Petra Borgcrantz, Thomas Arnström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Thomas Arnström, Petra Borgcrantz, Inger Persson, Per Muhr</t>
+          <t>Per Muhr, Inger Persson, Petra Borgcrantz, Thomas Arnström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 56047-2025 artfynd.xlsx
+++ b/artfynd/A 56047-2025 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>129985216</v>
       </c>
       <c r="B5" t="n">
-        <v>57896</v>
+        <v>57897</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>129997570</v>
       </c>
       <c r="B6" t="n">
-        <v>57896</v>
+        <v>57897</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>129985220</v>
       </c>
       <c r="B9" t="n">
-        <v>58419</v>
+        <v>58420</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 56047-2025 artfynd.xlsx
+++ b/artfynd/A 56047-2025 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>129985216</v>
       </c>
       <c r="B5" t="n">
-        <v>57898</v>
+        <v>57983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Per Muhr, Inger Persson, Petra Borgcrantz, Thomas Arnström</t>
+          <t>Thomas Arnström, Petra Borgcrantz, Inger Persson, Per Muhr</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1129,7 +1129,7 @@
         <v>129997570</v>
       </c>
       <c r="B6" t="n">
-        <v>57898</v>
+        <v>57983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>129985213</v>
       </c>
       <c r="B7" t="n">
-        <v>57754</v>
+        <v>57839</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Per Muhr, Inger Persson, Petra Borgcrantz, Thomas Arnström</t>
+          <t>Thomas Arnström, Petra Borgcrantz, Inger Persson, Per Muhr</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1358,7 +1358,7 @@
         <v>129985211</v>
       </c>
       <c r="B8" t="n">
-        <v>57678</v>
+        <v>57763</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Per Muhr, Inger Persson, Petra Borgcrantz, Thomas Arnström</t>
+          <t>Thomas Arnström, Petra Borgcrantz, Inger Persson, Per Muhr</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1473,7 +1473,7 @@
         <v>129985220</v>
       </c>
       <c r="B9" t="n">
-        <v>58421</v>
+        <v>58506</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Per Muhr, Inger Persson, Petra Borgcrantz, Thomas Arnström</t>
+          <t>Thomas Arnström, Petra Borgcrantz, Inger Persson, Per Muhr</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 56047-2025 artfynd.xlsx
+++ b/artfynd/A 56047-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1011,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129985216</v>
+        <v>129997570</v>
       </c>
       <c r="B5" t="n">
         <v>57983</v>
@@ -1046,21 +1046,25 @@
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ljungby, Sk</t>
+          <t>Slättåkra alsumpskog A56047-2025, Sk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>388160</v>
+        <v>388121</v>
       </c>
       <c r="R5" t="n">
-        <v>6213675</v>
+        <v>6213608</v>
       </c>
       <c r="S5" t="n">
-        <v>78</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1087,19 +1091,9 @@
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:12</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,39 +1108,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Per Muhr</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Per Muhr, Inger Persson, Petra Borgcrantz, Thomas Arnström</t>
+          <t>Petra Borgcrantz</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129997570</v>
+        <v>113768343</v>
       </c>
       <c r="B6" t="n">
-        <v>57983</v>
+        <v>57624</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103020</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1156,30 +1155,26 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Slättåkra alsumpskog A56047-2025, Sk</t>
+          <t>Slättåkra (Slättåkra), Sk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>388121</v>
+        <v>388189</v>
       </c>
       <c r="R6" t="n">
-        <v>6213608</v>
+        <v>6213746</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,12 +1198,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2023-12-27</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2023-12-27</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,585 +1218,15 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Bengt  Bengtsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Petra Borgcrantz</t>
+          <t>Bengt  Bengtsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>129985213</v>
-      </c>
-      <c r="B7" t="n">
-        <v>57839</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>100048</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Mindre hackspett</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Dryobates minor</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Ljungby, Sk</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>388160</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6213675</v>
-      </c>
-      <c r="S7" t="n">
-        <v>78</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Klippan</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Riseberga</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>10:12</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Högstubbar med bohål</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Per Muhr</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Per Muhr, Inger Persson, Petra Borgcrantz, Thomas Arnström</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>129985211</v>
-      </c>
-      <c r="B8" t="n">
-        <v>57763</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>100082</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Röd glada</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Milvus milvus</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Ljungby, Sk</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>388160</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6213675</v>
-      </c>
-      <c r="S8" t="n">
-        <v>78</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Klippan</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Riseberga</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:12</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:06</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Per Muhr</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Per Muhr, Inger Persson, Petra Borgcrantz, Thomas Arnström</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>129985220</v>
-      </c>
-      <c r="B9" t="n">
-        <v>58506</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>103044</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Grönsiska</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Spinus spinus</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Ljungby, Sk</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>388160</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6213675</v>
-      </c>
-      <c r="S9" t="n">
-        <v>78</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Klippan</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Riseberga</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:12</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2025-12-05</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>11:06</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Per Muhr</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Per Muhr, Inger Persson, Petra Borgcrantz, Thomas Arnström</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>113768313</v>
-      </c>
-      <c r="B10" t="n">
-        <v>57412</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>103020</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Entita</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Poecile palustris</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Slättåkra (Slättåkra), Sk</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>388253</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6213724</v>
-      </c>
-      <c r="S10" t="n">
-        <v>50</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Klippan</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Riseberga</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2023-12-27</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2023-12-27</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Bengt  Bengtsson</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Bengt  Bengtsson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>113768343</v>
-      </c>
-      <c r="B11" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>103015</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Regulus regulus</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Slättåkra (Slättåkra), Sk</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>388189</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6213746</v>
-      </c>
-      <c r="S11" t="n">
-        <v>50</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Klippan</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Skåne</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Riseberga</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2023-12-27</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2023-12-27</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Bengt  Bengtsson</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Bengt  Bengtsson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
